--- a/JsonConverter/ExcelFiles/Tower.xlsx
+++ b/JsonConverter/ExcelFiles/Tower.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7B0AF8-6EEF-408B-B01E-3B5490300070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F4257C-A038-40AA-BB68-A43DFB7ABA7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2865" yWindow="1860" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -36,10 +36,6 @@
     <t>Id</t>
   </si>
   <si>
-    <t>tower_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>tower_02</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -60,15 +56,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>공격 가능 대상</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>건설 비용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>판매 가격</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -211,10 +199,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Ground</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>AttackDamage</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -231,18 +215,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>MoveType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>BuildPrice</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>SellPrice</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>UpgradeId</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -290,17 +266,35 @@
     <t>Prefab/Tower/tower_05</t>
   </si>
   <si>
-    <t>tower_06</t>
-  </si>
-  <si>
-    <t>Prefab/Tower/tower_06</t>
-  </si>
-  <si>
-    <t>string[]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ground,Sky</t>
+    <t>투사체 프리팹 주소</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>stirng</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProjectilePath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tower_01_Level1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tower_01_Level2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tower_01_Level3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AbilityId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>특수능력 ID</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -423,7 +417,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -443,21 +437,6 @@
       </top>
       <bottom style="thin">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -482,9 +461,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -501,6 +477,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -719,130 +696,131 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:N1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="40" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" style="2" customWidth="1"/>
     <col min="12" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="12.75">
+      <c r="J1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="12.75">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="D3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="E3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="H3" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="I3" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="J3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>26</v>
-      </c>
       <c r="K3" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -856,242 +834,182 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>17</v>
-      </c>
+      <c r="F4" s="1"/>
       <c r="G4" s="1">
         <v>50</v>
       </c>
-      <c r="H4" s="1">
-        <v>25</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="1">
+      <c r="H4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1">
         <v>45</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>30</v>
-      </c>
+      <c r="J4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+    </row>
+    <row r="5" spans="1:14" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5">
-        <v>10</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="1">
-        <v>75</v>
-      </c>
-      <c r="H5" s="1">
-        <v>50</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="1">
-        <v>60</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>31</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="1">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" s="1">
-        <v>50</v>
-      </c>
-      <c r="H6" s="1">
-        <v>50</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="1">
-        <v>45</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>33</v>
-      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A7" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="1">
+    </row>
+    <row r="7" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5">
         <v>10</v>
       </c>
       <c r="C7" s="5">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="D7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="1">
-        <v>7</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="1">
-        <v>100</v>
-      </c>
-      <c r="H7" s="1">
         <v>75</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="1">
-        <v>45</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>35</v>
-      </c>
+      <c r="H7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="1">
+        <v>60</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>36</v>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="B8" s="1">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1">
         <v>5</v>
       </c>
-      <c r="C8" s="5">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
-        <v>7</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="F8" s="1"/>
       <c r="G8" s="1">
-        <v>100</v>
-      </c>
-      <c r="H8" s="1">
-        <v>75</v>
-      </c>
-      <c r="I8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="1">
+        <v>45</v>
+      </c>
+      <c r="J8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="1">
-        <v>46</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="16" t="s">
-        <v>38</v>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>28</v>
       </c>
       <c r="B9" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C9" s="5">
         <v>4</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" s="1">
         <v>7</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="F9" s="1"/>
       <c r="G9" s="1">
         <v>100</v>
       </c>
-      <c r="H9" s="1">
-        <v>75</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="1">
-        <v>47</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>39</v>
-      </c>
+      <c r="H9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="1">
+        <v>45</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A10" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>7</v>
+      </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="9"/>
+      <c r="G10" s="1">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="1">
+        <v>46</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+    </row>
+    <row r="11" spans="1:14" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1101,14 +1019,13 @@
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="9"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1">
+    </row>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1118,14 +1035,13 @@
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="9"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1">
+    </row>
+    <row r="13" spans="1:14" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1135,14 +1051,13 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="9"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1">
+    </row>
+    <row r="14" spans="1:14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1152,14 +1067,13 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="9"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1">
+    </row>
+    <row r="15" spans="1:14" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1169,27 +1083,25 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="9"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="9"/>
-    </row>
-    <row r="17" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" customHeight="1">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1199,10 +1111,9 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="9"/>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1212,10 +1123,9 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="9"/>
-    </row>
-    <row r="19" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" customHeight="1">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1225,10 +1135,9 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="9"/>
-    </row>
-    <row r="20" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J19" s="8"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1238,10 +1147,9 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="9"/>
-    </row>
-    <row r="21" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J20" s="8"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1251,10 +1159,9 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="9"/>
-    </row>
-    <row r="22" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J21" s="8"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1264,10 +1171,9 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="9"/>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J22" s="8"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1277,10 +1183,9 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="9"/>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J23" s="8"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1290,10 +1195,9 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="9"/>
-    </row>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J24" s="8"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1303,10 +1207,9 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="9"/>
-    </row>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1316,10 +1219,9 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="9"/>
-    </row>
-    <row r="27" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -1329,10 +1231,9 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="9"/>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -1342,10 +1243,9 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="9"/>
-    </row>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -1355,10 +1255,9 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="9"/>
-    </row>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -1368,10 +1267,9 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="9"/>
-    </row>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J30" s="8"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -1381,10 +1279,9 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="9"/>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1">
+      <c r="J31" s="8"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1394,8 +1291,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="9"/>
+      <c r="J32" s="8"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
       <c r="A33" s="7"/>

--- a/JsonConverter/ExcelFiles/Tower.xlsx
+++ b/JsonConverter/ExcelFiles/Tower.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="60">
   <si>
     <t xml:space="preserve">캐릭터 고유 ID</t>
   </si>
@@ -222,67 +222,332 @@
     <t xml:space="preserve">ProjectilePath</t>
   </si>
   <si>
-    <t xml:space="preserve">Tower_01_Level1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower_01_Level2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prefab/Tower/tower_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower_01_Level3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower_02_Level1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ddd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prefab/Tower/tower_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower_02_Level2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prefab/Tower/tower_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower_02_Level3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prefab/Tower/tower_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower_03_Level1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prefab/Tower/tower_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower_03_Level2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower_03_Level3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower_04_Level1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower_04_Level2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tower_04_Level3</t>
+    <t xml:space="preserve">Tower_Cheese_Level1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower_Cheese_Level2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/Tower/CheeseTower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/TowerProjectile/CheeseProjectile</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tower_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Cheese</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_Level2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower_Cheese_Level3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tower_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Cheese</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_Level3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower_Pepper_Level1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower_Pepper_Level2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/Tower/PepperTower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/TowerProjectile/PepperProjectile</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tower_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Pepper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_Level2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower_Pepper_Level3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tower_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Pepper</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_Level3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower_Ketchup_Level1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower_Ketchup_Level2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/Tower/KetchupTower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/TowerProjectile/KetchupProjectile</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tower_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Ketchup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_Level2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower_Ketchup_Level3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tower_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Ketchup</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_Level3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower_Oil_Level1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower_Oil_Level2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/Tower/OilTower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/TowerProjectile/OilProjectile</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tower_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Oil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_Level2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Tower_Oil_Level3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Tower_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">Oil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="&quot;맑은 고딕&quot;"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_Level3</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Tower_Salt_Level1</t>
   </si>
   <si>
-    <t xml:space="preserve">SaltDebuff</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tower_Salt_Level2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/Tower/SaltTower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/TowerProjectile/SaltProjectile</t>
   </si>
   <si>
     <t xml:space="preserve">Tower_Salt_Level3</t>
@@ -295,7 +560,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -363,6 +628,13 @@
       <family val="0"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -425,7 +697,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -466,12 +738,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -736,7 +1020,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="44.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="40.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="24.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="20.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="37.72"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="12.68"/>
   </cols>
   <sheetData>
@@ -853,19 +1137,19 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="10" t="s">
         <v>28</v>
       </c>
       <c r="I4" s="2" t="n">
@@ -874,383 +1158,463 @@
       <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="6"/>
+      <c r="K4" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B5" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C5" s="10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D5" s="10" t="n">
+      <c r="C5" s="11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1" t="n">
+      <c r="E5" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="6"/>
       <c r="L5" s="6"/>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="J6" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="K6" s="6"/>
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
-        <v>32</v>
+      <c r="G7" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="K7" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>37</v>
+      </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>32</v>
+      <c r="H8" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>37</v>
+      </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J9" s="4" t="s">
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
-        <v>32</v>
+      <c r="G10" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K10" s="6"/>
+        <v>50</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="6"/>
+      <c r="H11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="2"/>
+        <v>4.5</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="6"/>
+      <c r="J12" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>44</v>
+      </c>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="6"/>
+      <c r="G13" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="2"/>
+        <v>3.5</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="6"/>
+      <c r="H14" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>4.5</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="6"/>
+      <c r="J15" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>51</v>
+      </c>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="4"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>5.5</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>46</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="F17" s="10"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="4"/>
+      <c r="H17" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="E18" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>46</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F18" s="10"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="4"/>
+      <c r="J18" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>

--- a/JsonConverter/ExcelFiles/Tower.xlsx
+++ b/JsonConverter/ExcelFiles/Tower.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7B22C6-E59C-4A29-A550-8947D2F020DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D071BDEB-92B2-4368-BFF7-BA26FD714433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="63">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -559,6 +559,16 @@
   <si>
     <t>Prefabs/TowerProjectile/SaltProjectile</t>
     <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ability_01</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ability_02</t>
+  </si>
+  <si>
+    <t>Ability_03</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1298,9 @@
       <c r="E10" s="2">
         <v>15</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G10" s="2">
         <v>60</v>
       </c>
@@ -1324,7 +1336,9 @@
       <c r="E11" s="2">
         <v>17</v>
       </c>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="10" t="s">
         <v>39</v>
@@ -1358,7 +1372,9 @@
       <c r="E12" s="2">
         <v>20</v>
       </c>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1388,7 +1404,9 @@
       <c r="E13" s="2">
         <v>15</v>
       </c>
-      <c r="F13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="G13" s="2">
         <v>70</v>
       </c>
@@ -1424,7 +1442,9 @@
       <c r="E14" s="2">
         <v>17</v>
       </c>
-      <c r="F14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="G14" s="2"/>
       <c r="H14" s="10" t="s">
         <v>43</v>
@@ -1458,7 +1478,9 @@
       <c r="E15" s="2">
         <v>20</v>
       </c>
-      <c r="F15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1488,7 +1510,9 @@
       <c r="E16" s="2">
         <v>15</v>
       </c>
-      <c r="F16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="G16" s="2">
         <v>60</v>
       </c>
@@ -1521,7 +1545,9 @@
       <c r="E17" s="2">
         <v>17</v>
       </c>
-      <c r="F17" s="10"/>
+      <c r="F17" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="G17" s="2"/>
       <c r="H17" s="10" t="s">
         <v>47</v>
@@ -1552,7 +1578,9 @@
       <c r="E18" s="2">
         <v>20</v>
       </c>
-      <c r="F18" s="10"/>
+      <c r="F18" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
